--- a/research/traditional_assets/database/data/finland/finland_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_precious_metals.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.6940000000000001</v>
+        <v>-0.135</v>
       </c>
       <c r="G2">
-        <v>-510.7142857142857</v>
+        <v>-2.220394736842105</v>
       </c>
       <c r="H2">
-        <v>-510.7142857142857</v>
+        <v>-2.220394736842105</v>
       </c>
       <c r="I2">
-        <v>-732.1428571428571</v>
+        <v>-2.549342105263158</v>
       </c>
       <c r="J2">
-        <v>-732.1428571428571</v>
+        <v>-2.549342105263158</v>
       </c>
       <c r="K2">
-        <v>-26.5</v>
+        <v>-18.8</v>
       </c>
       <c r="L2">
-        <v>-946.4285714285714</v>
+        <v>-3.092105263157895</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>0.07258064516129033</v>
       </c>
       <c r="W2">
-        <v>-0.5216535433070867</v>
+        <v>-0.3636363636363636</v>
       </c>
       <c r="X2">
-        <v>0.0649740668454362</v>
+        <v>0.1347206872752227</v>
       </c>
       <c r="Y2">
-        <v>-0.5866276101525228</v>
+        <v>-0.4983570509115863</v>
       </c>
       <c r="Z2">
-        <v>0.0004416403785488959</v>
+        <v>0.1004460598050553</v>
       </c>
       <c r="AA2">
-        <v>-0.3233438485804416</v>
+        <v>-0.2560713695688088</v>
       </c>
       <c r="AB2">
-        <v>0.05871301848566139</v>
+        <v>0.1101331308910171</v>
       </c>
       <c r="AC2">
-        <v>-0.382056867066103</v>
+        <v>-0.3662045004598259</v>
       </c>
       <c r="AD2">
-        <v>11.8</v>
+        <v>19.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>11.8</v>
+        <v>19.6</v>
       </c>
       <c r="AG2">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="AH2">
-        <v>0.1569148936170213</v>
+        <v>0.2832369942196532</v>
       </c>
       <c r="AI2">
-        <v>0.1894060995184591</v>
+        <v>0.379110251450677</v>
       </c>
       <c r="AJ2">
-        <v>0.1569148936170213</v>
+        <v>0.2439024390243903</v>
       </c>
       <c r="AK2">
-        <v>0.1894060995184591</v>
+        <v>0.3326403326403326</v>
       </c>
       <c r="AL2">
-        <v>1.03</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="AM2">
-        <v>1.03</v>
+        <v>-6.289000000000001</v>
       </c>
       <c r="AN2">
-        <v>-0.5645933014354068</v>
+        <v>-1.675213675213675</v>
       </c>
       <c r="AO2">
-        <v>-19.90291262135922</v>
+        <v>-22.43125904486252</v>
       </c>
       <c r="AP2">
-        <v>-0.5645933014354068</v>
+        <v>-1.367521367521368</v>
       </c>
       <c r="AQ2">
-        <v>-19.90291262135922</v>
+        <v>2.464620766417554</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Endomines AB (publ) (OM:ENDO)</t>
+          <t>Endomines Finland Oyj (HLSE:PAMPALO)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.6940000000000001</v>
+        <v>-0.135</v>
       </c>
       <c r="G3">
-        <v>-510.7142857142857</v>
+        <v>-2.220394736842105</v>
       </c>
       <c r="H3">
-        <v>-510.7142857142857</v>
+        <v>-2.220394736842105</v>
       </c>
       <c r="I3">
-        <v>-732.1428571428571</v>
+        <v>-2.549342105263158</v>
       </c>
       <c r="J3">
-        <v>-732.1428571428571</v>
+        <v>-2.549342105263158</v>
       </c>
       <c r="K3">
-        <v>-26.5</v>
+        <v>-18.8</v>
       </c>
       <c r="L3">
-        <v>-946.4285714285714</v>
+        <v>-3.092105263157895</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.07258064516129033</v>
       </c>
       <c r="W3">
-        <v>-0.5216535433070867</v>
+        <v>-0.3636363636363636</v>
       </c>
       <c r="X3">
-        <v>0.0649740668454362</v>
+        <v>0.1347206872752227</v>
       </c>
       <c r="Y3">
-        <v>-0.5866276101525228</v>
+        <v>-0.4983570509115863</v>
       </c>
       <c r="Z3">
-        <v>0.0004416403785488959</v>
+        <v>0.1004460598050553</v>
       </c>
       <c r="AA3">
-        <v>-0.3233438485804416</v>
+        <v>-0.2560713695688088</v>
       </c>
       <c r="AB3">
-        <v>0.05871301848566139</v>
+        <v>0.1101331308910171</v>
       </c>
       <c r="AC3">
-        <v>-0.382056867066103</v>
+        <v>-0.3662045004598259</v>
       </c>
       <c r="AD3">
-        <v>11.8</v>
+        <v>19.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>11.8</v>
+        <v>19.6</v>
       </c>
       <c r="AG3">
-        <v>11.8</v>
+        <v>16</v>
       </c>
       <c r="AH3">
-        <v>0.1569148936170213</v>
+        <v>0.2832369942196532</v>
       </c>
       <c r="AI3">
-        <v>0.1894060995184591</v>
+        <v>0.379110251450677</v>
       </c>
       <c r="AJ3">
-        <v>0.1569148936170213</v>
+        <v>0.2439024390243903</v>
       </c>
       <c r="AK3">
-        <v>0.1894060995184591</v>
+        <v>0.3326403326403326</v>
       </c>
       <c r="AL3">
-        <v>1.03</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="AM3">
-        <v>1.03</v>
+        <v>-6.289000000000001</v>
       </c>
       <c r="AN3">
-        <v>-0.5645933014354068</v>
+        <v>-1.675213675213675</v>
       </c>
       <c r="AO3">
-        <v>-19.90291262135922</v>
+        <v>-22.43125904486252</v>
       </c>
       <c r="AP3">
-        <v>-0.5645933014354068</v>
+        <v>-1.367521367521368</v>
       </c>
       <c r="AQ3">
-        <v>-19.90291262135922</v>
+        <v>2.464620766417554</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/finland/finland_precious_metals.xlsx
+++ b/research/traditional_assets/database/data/finland/finland_precious_metals.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.135</v>
+        <v>0.114</v>
       </c>
       <c r="G2">
-        <v>-2.220394736842105</v>
+        <v>-0.3369458128078818</v>
       </c>
       <c r="H2">
-        <v>-2.220394736842105</v>
+        <v>-0.3369458128078818</v>
       </c>
       <c r="I2">
-        <v>-2.549342105263158</v>
+        <v>-0.4142857142857143</v>
       </c>
       <c r="J2">
-        <v>-2.549342105263158</v>
+        <v>-0.4142857142857143</v>
       </c>
       <c r="K2">
-        <v>-18.8</v>
+        <v>-11.7</v>
       </c>
       <c r="L2">
-        <v>-3.092105263157895</v>
+        <v>-0.5763546798029556</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.6</v>
+        <v>1.31</v>
       </c>
       <c r="V2">
-        <v>0.07258064516129033</v>
+        <v>0.02018489984591679</v>
       </c>
       <c r="W2">
-        <v>-0.3636363636363636</v>
+        <v>-0.3644859813084112</v>
       </c>
       <c r="X2">
-        <v>0.1347206872752227</v>
+        <v>0.1016660289232005</v>
       </c>
       <c r="Y2">
-        <v>-0.4983570509115863</v>
+        <v>-0.4661520102316117</v>
       </c>
       <c r="Z2">
-        <v>0.1004460598050553</v>
+        <v>0.4220374220374221</v>
       </c>
       <c r="AA2">
-        <v>-0.2560713695688088</v>
+        <v>-0.1748440748440749</v>
       </c>
       <c r="AB2">
-        <v>0.1101331308910171</v>
+        <v>0.09152340110566574</v>
       </c>
       <c r="AC2">
-        <v>-0.3662045004598259</v>
+        <v>-0.2663674759497406</v>
       </c>
       <c r="AD2">
-        <v>19.6</v>
+        <v>13.9</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>19.6</v>
+        <v>13.9</v>
       </c>
       <c r="AG2">
-        <v>16</v>
+        <v>12.59</v>
       </c>
       <c r="AH2">
-        <v>0.2832369942196532</v>
+        <v>0.1763959390862944</v>
       </c>
       <c r="AI2">
-        <v>0.379110251450677</v>
+        <v>0.2730844793713163</v>
       </c>
       <c r="AJ2">
-        <v>0.2439024390243903</v>
+        <v>0.1624725771067234</v>
       </c>
       <c r="AK2">
-        <v>0.3326403326403326</v>
+        <v>0.2538818310143174</v>
       </c>
       <c r="AL2">
-        <v>0.6909999999999999</v>
+        <v>3.56</v>
       </c>
       <c r="AM2">
-        <v>-6.289000000000001</v>
+        <v>3.56</v>
       </c>
       <c r="AN2">
-        <v>-1.675213675213675</v>
+        <v>-5.091575091575092</v>
       </c>
       <c r="AO2">
-        <v>-22.43125904486252</v>
+        <v>-2.362359550561798</v>
       </c>
       <c r="AP2">
-        <v>-1.367521367521368</v>
+        <v>-4.611721611721611</v>
       </c>
       <c r="AQ2">
-        <v>2.464620766417554</v>
+        <v>-2.362359550561798</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.135</v>
+        <v>0.114</v>
       </c>
       <c r="G3">
-        <v>-2.220394736842105</v>
+        <v>-0.3369458128078818</v>
       </c>
       <c r="H3">
-        <v>-2.220394736842105</v>
+        <v>-0.3369458128078818</v>
       </c>
       <c r="I3">
-        <v>-2.549342105263158</v>
+        <v>-0.4142857142857143</v>
       </c>
       <c r="J3">
-        <v>-2.549342105263158</v>
+        <v>-0.4142857142857143</v>
       </c>
       <c r="K3">
-        <v>-18.8</v>
+        <v>-11.7</v>
       </c>
       <c r="L3">
-        <v>-3.092105263157895</v>
+        <v>-0.5763546798029556</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.6</v>
+        <v>1.31</v>
       </c>
       <c r="V3">
-        <v>0.07258064516129033</v>
+        <v>0.02018489984591679</v>
       </c>
       <c r="W3">
-        <v>-0.3636363636363636</v>
+        <v>-0.3644859813084112</v>
       </c>
       <c r="X3">
-        <v>0.1347206872752227</v>
+        <v>0.1016660289232005</v>
       </c>
       <c r="Y3">
-        <v>-0.4983570509115863</v>
+        <v>-0.4661520102316117</v>
       </c>
       <c r="Z3">
-        <v>0.1004460598050553</v>
+        <v>0.4220374220374221</v>
       </c>
       <c r="AA3">
-        <v>-0.2560713695688088</v>
+        <v>-0.1748440748440749</v>
       </c>
       <c r="AB3">
-        <v>0.1101331308910171</v>
+        <v>0.09152340110566574</v>
       </c>
       <c r="AC3">
-        <v>-0.3662045004598259</v>
+        <v>-0.2663674759497406</v>
       </c>
       <c r="AD3">
-        <v>19.6</v>
+        <v>13.9</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>19.6</v>
+        <v>13.9</v>
       </c>
       <c r="AG3">
-        <v>16</v>
+        <v>12.59</v>
       </c>
       <c r="AH3">
-        <v>0.2832369942196532</v>
+        <v>0.1763959390862944</v>
       </c>
       <c r="AI3">
-        <v>0.379110251450677</v>
+        <v>0.2730844793713163</v>
       </c>
       <c r="AJ3">
-        <v>0.2439024390243903</v>
+        <v>0.1624725771067234</v>
       </c>
       <c r="AK3">
-        <v>0.3326403326403326</v>
+        <v>0.2538818310143174</v>
       </c>
       <c r="AL3">
-        <v>0.6909999999999999</v>
+        <v>3.56</v>
       </c>
       <c r="AM3">
-        <v>-6.289000000000001</v>
+        <v>3.56</v>
       </c>
       <c r="AN3">
-        <v>-1.675213675213675</v>
+        <v>-5.091575091575092</v>
       </c>
       <c r="AO3">
-        <v>-22.43125904486252</v>
+        <v>-2.362359550561798</v>
       </c>
       <c r="AP3">
-        <v>-1.367521367521368</v>
+        <v>-4.611721611721611</v>
       </c>
       <c r="AQ3">
-        <v>2.464620766417554</v>
+        <v>-2.362359550561798</v>
       </c>
     </row>
   </sheetData>
